--- a/Sindhi Muslim/Classes/Enrolment (G.R) of GHS Sindhi Jamait School Semis Code#408170153 (Class 1 to 8).xlsx
+++ b/Sindhi Muslim/Classes/Enrolment (G.R) of GHS Sindhi Jamait School Semis Code#408170153 (Class 1 to 8).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34AAD70-30C6-4C0D-9F90-C102733B4199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A54536-83C3-458D-9457-26FD6952B68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="515" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Grade 01 to 8'!$2:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/Sindhi Muslim/Classes/Enrolment (G.R) of GHS Sindhi Jamait School Semis Code#408170153 (Class 1 to 8).xlsx
+++ b/Sindhi Muslim/Classes/Enrolment (G.R) of GHS Sindhi Jamait School Semis Code#408170153 (Class 1 to 8).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A54536-83C3-458D-9457-26FD6952B68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6776722F-8623-4ABF-8A70-09069B8BC4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="515" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
